--- a/results/06-2026/beta/contributions-06-2026.xlsx
+++ b/results/06-2026/beta/contributions-06-2026.xlsx
@@ -2673,10 +2673,10 @@
         <v>0.000551965031565569</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.993610612244152</v>
+        <v>-0.563901926533413</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.400332757045023</v>
+        <v>-0.0293759286657161</v>
       </c>
       <c r="AA22" t="n">
         <v>-0.0973949910447126</v>
@@ -2771,10 +2771,10 @@
         <v>-0.0299392802978311</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.937821968966787</v>
+        <v>-0.941736425915037</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.531980090246069</v>
+        <v>0.535894547194319</v>
       </c>
       <c r="AA23" t="n">
         <v>-0.274529505412121</v>
@@ -2869,10 +2869,10 @@
         <v>0.0465164147221872</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.273885378533513</v>
+        <v>-1.02320131401768</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.275751448037125</v>
+        <v>1.02133524451407</v>
       </c>
       <c r="AA24" t="n">
         <v>-0.139229581720164</v>
@@ -2967,10 +2967,10 @@
         <v>0.0427711776553399</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.57957660760554</v>
+        <v>-1.56878037182218</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.261833944831957</v>
+        <v>0.251037709048592</v>
       </c>
       <c r="AA25" t="n">
         <v>-0.236364588453239</v>
@@ -3065,10 +3065,10 @@
         <v>0.0279219275040355</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.25947181449783</v>
+        <v>0.45679544563831</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.632213338315575</v>
+        <v>-0.0840539218205656</v>
       </c>
       <c r="AA26" t="n">
         <v>0.518830766937432</v>
@@ -3163,10 +3163,10 @@
         <v>0.0298460339594499</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.5671038059027</v>
+        <v>-0.310038277709138</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.144000003691044</v>
+        <v>-0.113065524502518</v>
       </c>
       <c r="AA27" t="n">
         <v>0.495558685442469</v>
@@ -3261,10 +3261,10 @@
         <v>-0.0327728224575521</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.320220152545529</v>
+        <v>-0.321933384762828</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.161629668840258</v>
+        <v>-0.159916436622958</v>
       </c>
       <c r="AA28" t="n">
         <v>0.259332692885168</v>
@@ -3359,10 +3359,10 @@
         <v>-0.0188333683503671</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.144054229428114</v>
+        <v>-0.145712300878208</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.161885268446017</v>
+        <v>-0.160227196995923</v>
       </c>
       <c r="AA29" t="n">
         <v>-0.0497318544737479</v>
@@ -3457,10 +3457,10 @@
         <v>-0.0237955709487201</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.138489424399087</v>
+        <v>-0.140129793493637</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.160775647597551</v>
+        <v>-0.159135278503001</v>
       </c>
       <c r="AA30" t="n">
         <v>-0.52205252025133</v>
@@ -3555,10 +3555,10 @@
         <v>-0.0120783940754789</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.121008626134354</v>
+        <v>-0.122605259151308</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.156456728074844</v>
+        <v>-0.15486009505789</v>
       </c>
       <c r="AA31" t="n">
         <v>-0.472376041617324</v>
@@ -3653,10 +3653,10 @@
         <v>-0.0227902971602149</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.126451889857658</v>
+        <v>-0.128004915214177</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.164869728202617</v>
+        <v>-0.163316702846099</v>
       </c>
       <c r="AA32" t="n">
         <v>-0.249918399898359</v>
@@ -3751,10 +3751,10 @@
         <v>-0.0119661510489623</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.192860170360113</v>
+        <v>-0.194375766997843</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.162294420893371</v>
+        <v>-0.160778824255641</v>
       </c>
       <c r="AA33" t="n">
         <v>-0.252151394022548</v>
@@ -3849,10 +3849,10 @@
         <v>0.00577189183083751</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.225108545398582</v>
+        <v>-0.226594695231705</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0.16203894718382</v>
+        <v>-0.160552797350697</v>
       </c>
       <c r="AA34" t="n">
         <v>-0.606161522208577</v>

--- a/results/06-2026/beta/contributions-06-2026.xlsx
+++ b/results/06-2026/beta/contributions-06-2026.xlsx
@@ -3106,7 +3106,7 @@
         <v>-0.177275710542129</v>
       </c>
       <c r="F27" t="n">
-        <v>0.121528970243519</v>
+        <v>0.0934153245580765</v>
       </c>
       <c r="G27" t="n">
         <v>-0.0296502192522053</v>
@@ -3169,22 +3169,22 @@
         <v>-0.113065524502518</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.495558685442469</v>
+        <v>0.467555812719875</v>
       </c>
       <c r="AB27" t="n">
         <v>-0.210068495709401</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.346584853288415</v>
+        <v>0.318520072724498</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.244089996852817</v>
+        <v>0.216087124130223</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.0765189489232416</v>
+        <v>-0.104583729487159</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.0395258909192063</v>
+        <v>-0.0465420860601855</v>
       </c>
     </row>
     <row r="28">
@@ -3204,7 +3204,7 @@
         <v>-0.176127949318067</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0550873494343489</v>
+        <v>0.0276004019594846</v>
       </c>
       <c r="G28" t="n">
         <v>-0.0281345637364049</v>
@@ -3267,22 +3267,22 @@
         <v>-0.159916436622958</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.259332692885168</v>
+        <v>0.23190505200772</v>
       </c>
       <c r="AB28" t="n">
         <v>-0.11344944776243</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.20619378956889</v>
+        <v>0.178733291340387</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.181425143618067</v>
+        <v>0.153997502740619</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.275656031816896</v>
+        <v>-0.3031165300454</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.173518630714225</v>
+        <v>-0.187399950412331</v>
       </c>
     </row>
     <row r="29">
@@ -3302,7 +3302,7 @@
         <v>-0.199823746473653</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.00019929095037767</v>
+        <v>-0.0134596169475721</v>
       </c>
       <c r="G29" t="n">
         <v>-0.0168163974913964</v>
@@ -3365,22 +3365,22 @@
         <v>-0.160227196995923</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.0497318544737479</v>
+        <v>-0.0629991340991395</v>
       </c>
       <c r="AB29" t="n">
         <v>-0.0816728725013126</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.0714477229295267</v>
+        <v>-0.0847264715812518</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.0025443668764997</v>
+        <v>-0.0107229127488918</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.377387220803658</v>
+        <v>-0.390665969455383</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.038194898251568</v>
+        <v>0.0209938913905315</v>
       </c>
     </row>
     <row r="30">
@@ -3400,7 +3400,7 @@
         <v>-0.18610015880645</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.268032786092446</v>
+        <v>-0.253688552873603</v>
       </c>
       <c r="G30" t="n">
         <v>-0.0163834111471112</v>
@@ -3463,22 +3463,22 @@
         <v>-0.159135278503001</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.52205252025133</v>
+        <v>-0.50766973421812</v>
       </c>
       <c r="AB30" t="n">
         <v>-0.00865652585666954</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.470757018499112</v>
+        <v>-0.456372911986712</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.255256447635832</v>
+        <v>-0.240873661602622</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.77002209049575</v>
+        <v>-0.75563798398335</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.374896073009886</v>
+        <v>-0.388501053242823</v>
       </c>
     </row>
     <row r="31">
@@ -3498,7 +3498,7 @@
         <v>-0.180630207192896</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.131970802297558</v>
+        <v>-0.1179177107918</v>
       </c>
       <c r="G31" t="n">
         <v>-0.0118967399948219</v>
@@ -3561,22 +3561,22 @@
         <v>-0.15486009505789</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.472376041617324</v>
+        <v>-0.458272130010322</v>
       </c>
       <c r="AB31" t="n">
         <v>0.0398427805528704</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.372332981737238</v>
+        <v>-0.358235045105774</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.108659366670345</v>
+        <v>-0.0945554550633428</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.649798335946436</v>
+        <v>-0.635700399314971</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.518215919765685</v>
+        <v>-0.521280220699776</v>
       </c>
     </row>
     <row r="32">
@@ -3596,7 +3596,7 @@
         <v>-0.187907680306217</v>
       </c>
       <c r="F32" t="n">
-        <v>0.113285402974249</v>
+        <v>0.113718617959926</v>
       </c>
       <c r="G32" t="n">
         <v>-0.00842644245736131</v>
@@ -3659,22 +3659,22 @@
         <v>-0.163316702846099</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.249918399898359</v>
+        <v>-0.249483509006717</v>
       </c>
       <c r="AB32" t="n">
         <v>-0.0388590418499953</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.288880728515349</v>
+        <v>-0.288445657970427</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.136398666383842</v>
+        <v>0.136833557275484</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.580202346575624</v>
+        <v>-0.579767276030702</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.594352498455367</v>
+        <v>-0.590442907196101</v>
       </c>
     </row>
     <row r="33">
@@ -3694,7 +3694,7 @@
         <v>-0.184381860922253</v>
       </c>
       <c r="F33" t="n">
-        <v>0.135482587160068</v>
+        <v>0.135905537440735</v>
       </c>
       <c r="G33" t="n">
         <v>0.00329475107119413</v>
@@ -3757,22 +3757,22 @@
         <v>-0.160778824255641</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.252151394022548</v>
+        <v>-0.251726694949662</v>
       </c>
       <c r="AB33" t="n">
         <v>0.0171152561285791</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.234990180772845</v>
+        <v>-0.234565559071119</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.176441298150528</v>
+        <v>0.176865997223414</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.590144772026329</v>
+        <v>-0.589720150324603</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.647541886261035</v>
+        <v>-0.640206452413406</v>
       </c>
     </row>
     <row r="34">
@@ -3792,7 +3792,7 @@
         <v>-0.183465051487523</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0137078445556185</v>
+        <v>-0.013293126608685</v>
       </c>
       <c r="G34" t="n">
         <v>0.00134440690092982</v>
@@ -3855,22 +3855,22 @@
         <v>-0.160552797350697</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.606161522208577</v>
+        <v>-0.60574419090177</v>
       </c>
       <c r="AB34" t="n">
         <v>-0.0438103805367445</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.650254388885584</v>
+        <v>-0.64983686330003</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.0105372194990532</v>
+        <v>0.0109545508058604</v>
       </c>
       <c r="AE34" t="n">
-        <v>-1.03740188146799</v>
+        <v>-1.03698435588243</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.714386834004094</v>
+        <v>-0.710543045388177</v>
       </c>
     </row>
   </sheetData>
